--- a/Data/EXCEL/Transfer/salemon/202208/9105-salemon-202208.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202208/9105-salemon-202208.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WORKSPACES\GoodinfoWebData\salemon\202208\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202208\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{616E2EBF-7950-4FBD-95C5-253132F6496D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{738D0B71-E8B1-4F38-B181-5B203FA51F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3510" yWindow="1395" windowWidth="22035" windowHeight="12855"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="30645" windowHeight="19905"/>
   </bookViews>
   <sheets>
     <sheet name="9105-salemon-202208" sheetId="2" r:id="rId1"/>
@@ -80,7 +80,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="25">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -246,7 +246,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -263,7 +263,7 @@
       <sz val="10"/>
       <color rgb="FF008000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -271,13 +271,21 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FFFF0000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -818,7 +826,7 @@
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -827,7 +835,7 @@
     <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="17" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -848,22 +856,22 @@
     <xf numFmtId="3" fontId="22" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1222,25 +1230,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q131"/>
-  <sheetFormatPr defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.125" customWidth="1"/>
-    <col min="2" max="3" width="8.625" customWidth="1"/>
-    <col min="4" max="4" width="10.25" customWidth="1"/>
-    <col min="5" max="5" width="8.625" customWidth="1"/>
-    <col min="6" max="6" width="9.625" customWidth="1"/>
-    <col min="7" max="7" width="11.25" customWidth="1"/>
-    <col min="8" max="8" width="10.25" customWidth="1"/>
-    <col min="9" max="10" width="9.625" customWidth="1"/>
-    <col min="11" max="11" width="10.25" customWidth="1"/>
-    <col min="12" max="12" width="9.625" customWidth="1"/>
-    <col min="13" max="13" width="10.25" customWidth="1"/>
-    <col min="14" max="15" width="9.625" customWidth="1"/>
-    <col min="16" max="16" width="10.25" customWidth="1"/>
-    <col min="17" max="17" width="11.375" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="3" width="13.625" customWidth="1"/>
+    <col min="4" max="4" width="14.25" customWidth="1"/>
+    <col min="5" max="6" width="13.625" customWidth="1"/>
+    <col min="7" max="7" width="15.625" customWidth="1"/>
+    <col min="8" max="8" width="14.25" customWidth="1"/>
+    <col min="9" max="10" width="13.625" customWidth="1"/>
+    <col min="11" max="11" width="14.25" customWidth="1"/>
+    <col min="12" max="12" width="13.625" customWidth="1"/>
+    <col min="13" max="13" width="14.25" customWidth="1"/>
+    <col min="14" max="15" width="13.625" customWidth="1"/>
+    <col min="16" max="16" width="14.25" customWidth="1"/>
+    <col min="17" max="17" width="14.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="1" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1267,7 +1274,7 @@
       <c r="P1" s="16"/>
       <c r="Q1" s="17"/>
     </row>
-    <row r="2" spans="1:17" s="1" customFormat="1" ht="16.5" customHeight="1">
+    <row r="2" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="13"/>
       <c r="B2" s="12" t="s">
         <v>4</v>
@@ -1306,7 +1313,7 @@
       </c>
       <c r="Q2" s="17"/>
     </row>
-    <row r="3" spans="1:17" s="1" customFormat="1">
+    <row r="3" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="13"/>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -1349,7 +1356,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="1" customFormat="1">
+    <row r="4" spans="1:17" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="14"/>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -1388,7 +1395,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="5" customFormat="1">
+    <row r="5" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>44743</v>
       </c>
@@ -1441,7 +1448,7 @@
         <v>25.7</v>
       </c>
     </row>
-    <row r="6" spans="1:17" s="5" customFormat="1">
+    <row r="6" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>44713</v>
       </c>
@@ -1494,7 +1501,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="7" spans="1:17" s="5" customFormat="1">
+    <row r="7" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>44682</v>
       </c>
@@ -1547,7 +1554,7 @@
         <v>23.3</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="5" customFormat="1">
+    <row r="8" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>44652</v>
       </c>
@@ -1600,7 +1607,7 @@
         <v>17.600000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:17" s="5" customFormat="1">
+    <row r="9" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>44621</v>
       </c>
@@ -1653,7 +1660,7 @@
         <v>20.6</v>
       </c>
     </row>
-    <row r="10" spans="1:17" s="5" customFormat="1">
+    <row r="10" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>44593</v>
       </c>
@@ -1706,7 +1713,7 @@
         <v>24.1</v>
       </c>
     </row>
-    <row r="11" spans="1:17" s="5" customFormat="1">
+    <row r="11" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>44562</v>
       </c>
@@ -1759,7 +1766,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="12" spans="1:17" s="5" customFormat="1">
+    <row r="12" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>44531</v>
       </c>
@@ -1812,7 +1819,7 @@
         <v>9.4700000000000006</v>
       </c>
     </row>
-    <row r="13" spans="1:17" s="5" customFormat="1">
+    <row r="13" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>44501</v>
       </c>
@@ -1865,7 +1872,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="14" spans="1:17" s="5" customFormat="1">
+    <row r="14" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>44470</v>
       </c>
@@ -1918,7 +1925,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="15" spans="1:17" s="5" customFormat="1">
+    <row r="15" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>44440</v>
       </c>
@@ -1971,7 +1978,7 @@
         <v>14.6</v>
       </c>
     </row>
-    <row r="16" spans="1:17" s="5" customFormat="1">
+    <row r="16" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>44409</v>
       </c>
@@ -2024,7 +2031,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="5" customFormat="1">
+    <row r="17" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>44378</v>
       </c>
@@ -2077,7 +2084,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="5" customFormat="1">
+    <row r="18" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>44348</v>
       </c>
@@ -2130,7 +2137,7 @@
         <v>22.3</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="5" customFormat="1">
+    <row r="19" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>44317</v>
       </c>
@@ -2183,7 +2190,7 @@
         <v>28.4</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="5" customFormat="1">
+    <row r="20" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>44287</v>
       </c>
@@ -2236,7 +2243,7 @@
         <v>37.200000000000003</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="5" customFormat="1">
+    <row r="21" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>44256</v>
       </c>
@@ -2289,7 +2296,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="5" customFormat="1">
+    <row r="22" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>44228</v>
       </c>
@@ -2342,7 +2349,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="23" spans="1:17" s="5" customFormat="1">
+    <row r="23" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>44197</v>
       </c>
@@ -2395,7 +2402,7 @@
         <v>17.899999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:17" s="5" customFormat="1">
+    <row r="24" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>44166</v>
       </c>
@@ -2448,7 +2455,7 @@
         <v>-3.99</v>
       </c>
     </row>
-    <row r="25" spans="1:17" s="5" customFormat="1">
+    <row r="25" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>44136</v>
       </c>
@@ -2501,7 +2508,7 @@
         <v>-6.74</v>
       </c>
     </row>
-    <row r="26" spans="1:17" s="5" customFormat="1">
+    <row r="26" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>44105</v>
       </c>
@@ -2554,7 +2561,7 @@
         <v>-8.42</v>
       </c>
     </row>
-    <row r="27" spans="1:17" s="5" customFormat="1">
+    <row r="27" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>44075</v>
       </c>
@@ -2607,7 +2614,7 @@
         <v>-11.2</v>
       </c>
     </row>
-    <row r="28" spans="1:17" s="5" customFormat="1">
+    <row r="28" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>44044</v>
       </c>
@@ -2660,7 +2667,7 @@
         <v>-14.7</v>
       </c>
     </row>
-    <row r="29" spans="1:17" s="5" customFormat="1">
+    <row r="29" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>44013</v>
       </c>
@@ -2713,7 +2720,7 @@
         <v>-16.600000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:17" s="5" customFormat="1">
+    <row r="30" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>43983</v>
       </c>
@@ -2766,7 +2773,7 @@
         <v>-18.5</v>
       </c>
     </row>
-    <row r="31" spans="1:17" s="5" customFormat="1">
+    <row r="31" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>43952</v>
       </c>
@@ -2819,7 +2826,7 @@
         <v>-21.4</v>
       </c>
     </row>
-    <row r="32" spans="1:17" s="5" customFormat="1">
+    <row r="32" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>43922</v>
       </c>
@@ -2872,7 +2879,7 @@
         <v>-23.7</v>
       </c>
     </row>
-    <row r="33" spans="1:17" s="5" customFormat="1">
+    <row r="33" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>43891</v>
       </c>
@@ -2925,7 +2932,7 @@
         <v>-20.3</v>
       </c>
     </row>
-    <row r="34" spans="1:17" s="5" customFormat="1">
+    <row r="34" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>43862</v>
       </c>
@@ -2978,7 +2985,7 @@
         <v>-20.8</v>
       </c>
     </row>
-    <row r="35" spans="1:17" s="5" customFormat="1">
+    <row r="35" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>43831</v>
       </c>
@@ -3031,7 +3038,7 @@
         <v>-22.9</v>
       </c>
     </row>
-    <row r="36" spans="1:17" s="5" customFormat="1">
+    <row r="36" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="6">
         <v>43800</v>
       </c>
@@ -3084,7 +3091,7 @@
         <v>-2.89</v>
       </c>
     </row>
-    <row r="37" spans="1:17" s="5" customFormat="1">
+    <row r="37" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="6">
         <v>43770</v>
       </c>
@@ -3137,7 +3144,7 @@
         <v>-1.51</v>
       </c>
     </row>
-    <row r="38" spans="1:17" s="5" customFormat="1">
+    <row r="38" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="6">
         <v>43739</v>
       </c>
@@ -3190,7 +3197,7 @@
         <v>0.72</v>
       </c>
     </row>
-    <row r="39" spans="1:17" s="5" customFormat="1">
+    <row r="39" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="6">
         <v>43709</v>
       </c>
@@ -3243,7 +3250,7 @@
         <v>3.01</v>
       </c>
     </row>
-    <row r="40" spans="1:17" s="5" customFormat="1">
+    <row r="40" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="6">
         <v>43678</v>
       </c>
@@ -3296,7 +3303,7 @@
         <v>5.23</v>
       </c>
     </row>
-    <row r="41" spans="1:17" s="5" customFormat="1">
+    <row r="41" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="6">
         <v>43647</v>
       </c>
@@ -3349,7 +3356,7 @@
         <v>7.08</v>
       </c>
     </row>
-    <row r="42" spans="1:17" s="5" customFormat="1">
+    <row r="42" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="6">
         <v>43617</v>
       </c>
@@ -3402,7 +3409,7 @@
         <v>7.71</v>
       </c>
     </row>
-    <row r="43" spans="1:17" s="5" customFormat="1">
+    <row r="43" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="6">
         <v>43586</v>
       </c>
@@ -3455,7 +3462,7 @@
         <v>9.1199999999999992</v>
       </c>
     </row>
-    <row r="44" spans="1:17" s="5" customFormat="1">
+    <row r="44" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="6">
         <v>43556</v>
       </c>
@@ -3508,7 +3515,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="45" spans="1:17" s="5" customFormat="1">
+    <row r="45" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="6">
         <v>43525</v>
       </c>
@@ -3561,7 +3568,7 @@
         <v>13.6</v>
       </c>
     </row>
-    <row r="46" spans="1:17" s="5" customFormat="1">
+    <row r="46" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="6">
         <v>43497</v>
       </c>
@@ -3614,7 +3621,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="47" spans="1:17" s="5" customFormat="1">
+    <row r="47" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="6">
         <v>43466</v>
       </c>
@@ -3667,7 +3674,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="48" spans="1:17" s="5" customFormat="1">
+    <row r="48" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="6">
         <v>43435</v>
       </c>
@@ -3720,7 +3727,7 @@
         <v>9.52</v>
       </c>
     </row>
-    <row r="49" spans="1:17" s="5" customFormat="1">
+    <row r="49" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="6">
         <v>43405</v>
       </c>
@@ -3773,7 +3780,7 @@
         <v>9.74</v>
       </c>
     </row>
-    <row r="50" spans="1:17" s="5" customFormat="1">
+    <row r="50" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>43374</v>
       </c>
@@ -3826,7 +3833,7 @@
         <v>9.7799999999999994</v>
       </c>
     </row>
-    <row r="51" spans="1:17" s="5" customFormat="1">
+    <row r="51" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="6">
         <v>43344</v>
       </c>
@@ -3879,7 +3886,7 @@
         <v>8.83</v>
       </c>
     </row>
-    <row r="52" spans="1:17" s="5" customFormat="1">
+    <row r="52" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="6">
         <v>43313</v>
       </c>
@@ -3932,7 +3939,7 @@
         <v>8.5299999999999994</v>
       </c>
     </row>
-    <row r="53" spans="1:17" s="5" customFormat="1">
+    <row r="53" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="6">
         <v>43282</v>
       </c>
@@ -3985,7 +3992,7 @@
         <v>8.67</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="5" customFormat="1">
+    <row r="54" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="6">
         <v>43252</v>
       </c>
@@ -4038,7 +4045,7 @@
         <v>8.7899999999999991</v>
       </c>
     </row>
-    <row r="55" spans="1:17" s="5" customFormat="1">
+    <row r="55" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="6">
         <v>43221</v>
       </c>
@@ -4091,7 +4098,7 @@
         <v>7.44</v>
       </c>
     </row>
-    <row r="56" spans="1:17" s="5" customFormat="1">
+    <row r="56" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="6">
         <v>43191</v>
       </c>
@@ -4144,7 +4151,7 @@
         <v>4.84</v>
       </c>
     </row>
-    <row r="57" spans="1:17" s="5" customFormat="1">
+    <row r="57" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="6">
         <v>43160</v>
       </c>
@@ -4197,7 +4204,7 @@
         <v>1.84</v>
       </c>
     </row>
-    <row r="58" spans="1:17" s="5" customFormat="1">
+    <row r="58" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="6">
         <v>43132</v>
       </c>
@@ -4250,7 +4257,7 @@
         <v>0.99</v>
       </c>
     </row>
-    <row r="59" spans="1:17" s="5" customFormat="1">
+    <row r="59" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="6">
         <v>43101</v>
       </c>
@@ -4303,7 +4310,7 @@
         <v>1.41</v>
       </c>
     </row>
-    <row r="60" spans="1:17" s="5" customFormat="1">
+    <row r="60" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="6">
         <v>43070</v>
       </c>
@@ -4356,7 +4363,7 @@
         <v>-2.12</v>
       </c>
     </row>
-    <row r="61" spans="1:17" s="5" customFormat="1">
+    <row r="61" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="6">
         <v>43040</v>
       </c>
@@ -4409,7 +4416,7 @@
         <v>-3.05</v>
       </c>
     </row>
-    <row r="62" spans="1:17" s="5" customFormat="1">
+    <row r="62" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A62" s="6">
         <v>43009</v>
       </c>
@@ -4462,7 +4469,7 @@
         <v>-4.2300000000000004</v>
       </c>
     </row>
-    <row r="63" spans="1:17" s="5" customFormat="1">
+    <row r="63" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A63" s="6">
         <v>42979</v>
       </c>
@@ -4515,7 +4522,7 @@
         <v>-5.73</v>
       </c>
     </row>
-    <row r="64" spans="1:17" s="5" customFormat="1">
+    <row r="64" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A64" s="6">
         <v>42948</v>
       </c>
@@ -4568,7 +4575,7 @@
         <v>-6.32</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="5" customFormat="1">
+    <row r="65" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A65" s="6">
         <v>42917</v>
       </c>
@@ -4621,7 +4628,7 @@
         <v>-6.2</v>
       </c>
     </row>
-    <row r="66" spans="1:17" s="5" customFormat="1">
+    <row r="66" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>42887</v>
       </c>
@@ -4674,7 +4681,7 @@
         <v>-6.34</v>
       </c>
     </row>
-    <row r="67" spans="1:17" s="5" customFormat="1">
+    <row r="67" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A67" s="6">
         <v>42856</v>
       </c>
@@ -4727,7 +4734,7 @@
         <v>-4.88</v>
       </c>
     </row>
-    <row r="68" spans="1:17" s="5" customFormat="1">
+    <row r="68" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A68" s="6">
         <v>42826</v>
       </c>
@@ -4780,7 +4787,7 @@
         <v>-3.52</v>
       </c>
     </row>
-    <row r="69" spans="1:17" s="5" customFormat="1">
+    <row r="69" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A69" s="6">
         <v>42795</v>
       </c>
@@ -4833,7 +4840,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="70" spans="1:17" s="5" customFormat="1">
+    <row r="70" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A70" s="6">
         <v>42767</v>
       </c>
@@ -4886,7 +4893,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="71" spans="1:17" s="5" customFormat="1">
+    <row r="71" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A71" s="6">
         <v>42736</v>
       </c>
@@ -4939,7 +4946,7 @@
         <v>-3.8</v>
       </c>
     </row>
-    <row r="72" spans="1:17" s="5" customFormat="1">
+    <row r="72" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A72" s="6">
         <v>42705</v>
       </c>
@@ -4992,7 +4999,7 @@
         <v>-24.2</v>
       </c>
     </row>
-    <row r="73" spans="1:17" s="5" customFormat="1">
+    <row r="73" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A73" s="6">
         <v>42675</v>
       </c>
@@ -5045,7 +5052,7 @@
         <v>-29.8</v>
       </c>
     </row>
-    <row r="74" spans="1:17" s="5" customFormat="1">
+    <row r="74" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A74" s="6">
         <v>42644</v>
       </c>
@@ -5098,7 +5105,7 @@
         <v>-30.8</v>
       </c>
     </row>
-    <row r="75" spans="1:17" s="5" customFormat="1">
+    <row r="75" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A75" s="6">
         <v>42614</v>
       </c>
@@ -5151,7 +5158,7 @@
         <v>-30.6</v>
       </c>
     </row>
-    <row r="76" spans="1:17" s="5" customFormat="1">
+    <row r="76" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A76" s="6">
         <v>42583</v>
       </c>
@@ -5204,7 +5211,7 @@
         <v>-31</v>
       </c>
     </row>
-    <row r="77" spans="1:17" s="5" customFormat="1">
+    <row r="77" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A77" s="6">
         <v>42552</v>
       </c>
@@ -5257,7 +5264,7 @@
         <v>-32.9</v>
       </c>
     </row>
-    <row r="78" spans="1:17" s="5" customFormat="1">
+    <row r="78" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A78" s="6">
         <v>42522</v>
       </c>
@@ -5310,7 +5317,7 @@
         <v>-34.200000000000003</v>
       </c>
     </row>
-    <row r="79" spans="1:17" s="5" customFormat="1">
+    <row r="79" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A79" s="6">
         <v>42491</v>
       </c>
@@ -5363,7 +5370,7 @@
         <v>-36.5</v>
       </c>
     </row>
-    <row r="80" spans="1:17" s="5" customFormat="1">
+    <row r="80" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A80" s="6">
         <v>42461</v>
       </c>
@@ -5416,7 +5423,7 @@
         <v>-39.299999999999997</v>
       </c>
     </row>
-    <row r="81" spans="1:17" s="5" customFormat="1">
+    <row r="81" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A81" s="6">
         <v>42430</v>
       </c>
@@ -5469,7 +5476,7 @@
         <v>-42.3</v>
       </c>
     </row>
-    <row r="82" spans="1:17" s="5" customFormat="1">
+    <row r="82" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A82" s="6">
         <v>42401</v>
       </c>
@@ -5522,7 +5529,7 @@
         <v>-43.9</v>
       </c>
     </row>
-    <row r="83" spans="1:17" s="5" customFormat="1">
+    <row r="83" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A83" s="6">
         <v>42370</v>
       </c>
@@ -5575,7 +5582,7 @@
         <v>-44.1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" s="5" customFormat="1">
+    <row r="84" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A84" s="6">
         <v>42339</v>
       </c>
@@ -5628,7 +5635,7 @@
         <v>-7.95</v>
       </c>
     </row>
-    <row r="85" spans="1:17" s="5" customFormat="1">
+    <row r="85" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A85" s="6">
         <v>42309</v>
       </c>
@@ -5681,7 +5688,7 @@
         <v>2.25</v>
       </c>
     </row>
-    <row r="86" spans="1:17" s="5" customFormat="1">
+    <row r="86" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A86" s="6">
         <v>42278</v>
       </c>
@@ -5734,7 +5741,7 @@
         <v>6.47</v>
       </c>
     </row>
-    <row r="87" spans="1:17" s="5" customFormat="1">
+    <row r="87" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A87" s="6">
         <v>42248</v>
       </c>
@@ -5787,7 +5794,7 @@
         <v>9.15</v>
       </c>
     </row>
-    <row r="88" spans="1:17" s="5" customFormat="1">
+    <row r="88" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A88" s="6">
         <v>42217</v>
       </c>
@@ -5840,7 +5847,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="89" spans="1:17" s="5" customFormat="1">
+    <row r="89" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A89" s="6">
         <v>42186</v>
       </c>
@@ -5893,7 +5900,7 @@
         <v>15.2</v>
       </c>
     </row>
-    <row r="90" spans="1:17" s="5" customFormat="1">
+    <row r="90" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A90" s="6">
         <v>42156</v>
       </c>
@@ -5946,7 +5953,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="91" spans="1:17" s="5" customFormat="1">
+    <row r="91" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A91" s="6">
         <v>42125</v>
       </c>
@@ -5999,7 +6006,7 @@
         <v>22.1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" s="5" customFormat="1">
+    <row r="92" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A92" s="6">
         <v>42095</v>
       </c>
@@ -6052,7 +6059,7 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="93" spans="1:17" s="5" customFormat="1">
+    <row r="93" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A93" s="6">
         <v>42064</v>
       </c>
@@ -6105,7 +6112,7 @@
         <v>34.200000000000003</v>
       </c>
     </row>
-    <row r="94" spans="1:17" s="5" customFormat="1">
+    <row r="94" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A94" s="6">
         <v>42036</v>
       </c>
@@ -6158,7 +6165,7 @@
         <v>35.4</v>
       </c>
     </row>
-    <row r="95" spans="1:17" s="5" customFormat="1">
+    <row r="95" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A95" s="6">
         <v>42005</v>
       </c>
@@ -6211,7 +6218,7 @@
         <v>34.4</v>
       </c>
     </row>
-    <row r="96" spans="1:17" s="5" customFormat="1">
+    <row r="96" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A96" s="6">
         <v>41974</v>
       </c>
@@ -6264,7 +6271,7 @@
         <v>19.399999999999999</v>
       </c>
     </row>
-    <row r="97" spans="1:17" s="5" customFormat="1">
+    <row r="97" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>41944</v>
       </c>
@@ -6317,7 +6324,7 @@
         <v>16.600000000000001</v>
       </c>
     </row>
-    <row r="98" spans="1:17" s="5" customFormat="1">
+    <row r="98" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A98" s="6">
         <v>41913</v>
       </c>
@@ -6370,7 +6377,7 @@
         <v>12.4</v>
       </c>
     </row>
-    <row r="99" spans="1:17" s="5" customFormat="1">
+    <row r="99" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A99" s="6">
         <v>41883</v>
       </c>
@@ -6423,7 +6430,7 @@
         <v>8.8800000000000008</v>
       </c>
     </row>
-    <row r="100" spans="1:17" s="5" customFormat="1">
+    <row r="100" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A100" s="6">
         <v>41852</v>
       </c>
@@ -6476,7 +6483,7 @@
         <v>4.51</v>
       </c>
     </row>
-    <row r="101" spans="1:17" s="5" customFormat="1">
+    <row r="101" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A101" s="6">
         <v>41821</v>
       </c>
@@ -6529,7 +6536,7 @@
         <v>0.79</v>
       </c>
     </row>
-    <row r="102" spans="1:17" s="5" customFormat="1">
+    <row r="102" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A102" s="6">
         <v>41791</v>
       </c>
@@ -6582,7 +6589,7 @@
         <v>-1.04</v>
       </c>
     </row>
-    <row r="103" spans="1:17" s="5" customFormat="1">
+    <row r="103" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A103" s="6">
         <v>41760</v>
       </c>
@@ -6635,7 +6642,7 @@
         <v>-2.17</v>
       </c>
     </row>
-    <row r="104" spans="1:17" s="5" customFormat="1">
+    <row r="104" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A104" s="6">
         <v>41730</v>
       </c>
@@ -6688,7 +6695,7 @@
         <v>-5.96</v>
       </c>
     </row>
-    <row r="105" spans="1:17" s="5" customFormat="1">
+    <row r="105" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A105" s="6">
         <v>41699</v>
       </c>
@@ -6741,7 +6748,7 @@
         <v>-8.06</v>
       </c>
     </row>
-    <row r="106" spans="1:17" s="5" customFormat="1">
+    <row r="106" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A106" s="6">
         <v>41671</v>
       </c>
@@ -6794,7 +6801,7 @@
         <v>-3.51</v>
       </c>
     </row>
-    <row r="107" spans="1:17" s="5" customFormat="1">
+    <row r="107" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
         <v>41640</v>
       </c>
@@ -6847,7 +6854,7 @@
         <v>-5.93</v>
       </c>
     </row>
-    <row r="108" spans="1:17" s="5" customFormat="1">
+    <row r="108" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A108" s="6">
         <v>41609</v>
       </c>
@@ -6900,7 +6907,7 @@
         <v>-9.7799999999999994</v>
       </c>
     </row>
-    <row r="109" spans="1:17" s="5" customFormat="1">
+    <row r="109" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A109" s="6">
         <v>41579</v>
       </c>
@@ -6953,7 +6960,7 @@
         <v>-13.9</v>
       </c>
     </row>
-    <row r="110" spans="1:17" s="5" customFormat="1">
+    <row r="110" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A110" s="6">
         <v>41548</v>
       </c>
@@ -7006,7 +7013,7 @@
         <v>-13.5</v>
       </c>
     </row>
-    <row r="111" spans="1:17" s="5" customFormat="1">
+    <row r="111" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A111" s="6">
         <v>41518</v>
       </c>
@@ -7059,7 +7066,7 @@
         <v>-12.3</v>
       </c>
     </row>
-    <row r="112" spans="1:17" s="5" customFormat="1">
+    <row r="112" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A112" s="6">
         <v>41487</v>
       </c>
@@ -7112,7 +7119,7 @@
         <v>-13.5</v>
       </c>
     </row>
-    <row r="113" spans="1:17" s="5" customFormat="1">
+    <row r="113" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A113" s="6">
         <v>41456</v>
       </c>
@@ -7165,7 +7172,7 @@
         <v>-11</v>
       </c>
     </row>
-    <row r="114" spans="1:17" s="5" customFormat="1">
+    <row r="114" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A114" s="6">
         <v>41426</v>
       </c>
@@ -7218,7 +7225,7 @@
         <v>-10.1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" s="5" customFormat="1">
+    <row r="115" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
         <v>41395</v>
       </c>
@@ -7271,7 +7278,7 @@
         <v>-12.4</v>
       </c>
     </row>
-    <row r="116" spans="1:17" s="5" customFormat="1">
+    <row r="116" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A116" s="6">
         <v>41365</v>
       </c>
@@ -7324,7 +7331,7 @@
         <v>-9.93</v>
       </c>
     </row>
-    <row r="117" spans="1:17" s="5" customFormat="1">
+    <row r="117" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A117" s="6">
         <v>41334</v>
       </c>
@@ -7377,7 +7384,7 @@
         <v>-9.4600000000000009</v>
       </c>
     </row>
-    <row r="118" spans="1:17" s="5" customFormat="1">
+    <row r="118" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A118" s="6">
         <v>41306</v>
       </c>
@@ -7430,7 +7437,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="119" spans="1:17" s="5" customFormat="1">
+    <row r="119" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A119" s="6">
         <v>41275</v>
       </c>
@@ -7483,7 +7490,7 @@
         <v>13.9</v>
       </c>
     </row>
-    <row r="120" spans="1:17" s="5" customFormat="1">
+    <row r="120" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
         <v>41244</v>
       </c>
@@ -7536,7 +7543,7 @@
         <v>6.61</v>
       </c>
     </row>
-    <row r="121" spans="1:17" s="5" customFormat="1">
+    <row r="121" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A121" s="6">
         <v>41214</v>
       </c>
@@ -7589,7 +7596,7 @@
         <v>8.76</v>
       </c>
     </row>
-    <row r="122" spans="1:17" s="5" customFormat="1">
+    <row r="122" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A122" s="6">
         <v>41183</v>
       </c>
@@ -7642,7 +7649,7 @@
         <v>9.49</v>
       </c>
     </row>
-    <row r="123" spans="1:17" s="5" customFormat="1">
+    <row r="123" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A123" s="6">
         <v>41153</v>
       </c>
@@ -7695,7 +7702,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="124" spans="1:17" s="5" customFormat="1">
+    <row r="124" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
         <v>41122</v>
       </c>
@@ -7748,7 +7755,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="125" spans="1:17" s="5" customFormat="1">
+    <row r="125" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A125" s="6">
         <v>41091</v>
       </c>
@@ -7801,7 +7808,7 @@
         <v>13.3</v>
       </c>
     </row>
-    <row r="126" spans="1:17" s="5" customFormat="1">
+    <row r="126" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A126" s="6">
         <v>41061</v>
       </c>
@@ -7854,7 +7861,7 @@
         <v>13.7</v>
       </c>
     </row>
-    <row r="127" spans="1:17" s="5" customFormat="1">
+    <row r="127" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A127" s="6">
         <v>41030</v>
       </c>
@@ -7907,7 +7914,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="128" spans="1:17" s="5" customFormat="1">
+    <row r="128" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
         <v>41000</v>
       </c>
@@ -7960,7 +7967,7 @@
         <v>17.7</v>
       </c>
     </row>
-    <row r="129" spans="1:17" s="5" customFormat="1">
+    <row r="129" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A129" s="6">
         <v>40969</v>
       </c>
@@ -8013,7 +8020,7 @@
         <v>12.7</v>
       </c>
     </row>
-    <row r="130" spans="1:17" s="5" customFormat="1">
+    <row r="130" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A130" s="6">
         <v>40940</v>
       </c>
@@ -8066,7 +8073,7 @@
         <v>3.74</v>
       </c>
     </row>
-    <row r="131" spans="1:17" s="5" customFormat="1">
+    <row r="131" spans="1:17" s="5" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A131" s="6">
         <v>40909</v>
       </c>
@@ -8134,7 +8141,7 @@
     <mergeCell ref="H2:J2"/>
     <mergeCell ref="K2:L2"/>
   </mergeCells>
-  <phoneticPr fontId="24" type="noConversion"/>
+  <phoneticPr fontId="25" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>